--- a/download/PnL_Sample_Data.xlsx
+++ b/download/PnL_Sample_Data.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="الراجحي" sheetId="1" r:id="rId1"/>
     <sheet name="الإنماء" sheetId="2" r:id="rId2"/>
+    <sheet name="الرياض" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,10 +399,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:E17"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -409,166 +413,294 @@
         <v>البند Line Item</v>
       </c>
       <c r="B1" t="str">
-        <v>القيمة Value</v>
+        <v>Q1 2024</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Q2 2024</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Q3 2024</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Q4 2024</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>العملة Currency</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>SAR</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SAR</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>الفترة المالية Period</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Q1 2024</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>العملة Currency</v>
-      </c>
-      <c r="B4" t="str">
-        <v>SAR</v>
+        <v>الإيرادات - Revenue</v>
+      </c>
+      <c r="B4">
+        <v>15000000000</v>
+      </c>
+      <c r="C4">
+        <v>16200000000</v>
+      </c>
+      <c r="D4">
+        <v>15800000000</v>
+      </c>
+      <c r="E4">
+        <v>17500000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+        <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
+      </c>
+      <c r="B5">
+        <v>3200000000</v>
+      </c>
+      <c r="C5">
+        <v>3500000000</v>
+      </c>
+      <c r="D5">
+        <v>3400000000</v>
+      </c>
+      <c r="E5">
+        <v>3800000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>الإيرادات - Revenue</v>
+        <v>إجمالي الربح - Gross Profit</v>
       </c>
       <c r="B6">
-        <v>15000000000</v>
+        <v>11800000000</v>
+      </c>
+      <c r="C6">
+        <v>12700000000</v>
+      </c>
+      <c r="D6">
+        <v>12400000000</v>
+      </c>
+      <c r="E6">
+        <v>13700000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
+        <v>المصروفات التشغيلية - Operating Expenses</v>
       </c>
       <c r="B7">
-        <v>3200000000</v>
+        <v>5800000000</v>
+      </c>
+      <c r="C7">
+        <v>6100000000</v>
+      </c>
+      <c r="D7">
+        <v>5900000000</v>
+      </c>
+      <c r="E7">
+        <v>6500000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>إجمالي الربح - Gross Profit</v>
+        <v>مصروفات البيع - Selling Expenses</v>
       </c>
       <c r="B8">
-        <v>11800000000</v>
+        <v>1200000000</v>
+      </c>
+      <c r="C8">
+        <v>1300000000</v>
+      </c>
+      <c r="D8">
+        <v>1250000000</v>
+      </c>
+      <c r="E8">
+        <v>1400000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>المصروفات التشغيلية - Operating Expenses</v>
+        <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
       </c>
       <c r="B9">
-        <v>5800000000</v>
+        <v>2100000000</v>
+      </c>
+      <c r="C9">
+        <v>2200000000</v>
+      </c>
+      <c r="D9">
+        <v>2150000000</v>
+      </c>
+      <c r="E9">
+        <v>2400000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>مصروفات البيع - Selling Expenses</v>
+        <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
       </c>
       <c r="B10">
-        <v>1200000000</v>
+        <v>2500000000</v>
+      </c>
+      <c r="C10">
+        <v>2600000000</v>
+      </c>
+      <c r="D10">
+        <v>2500000000</v>
+      </c>
+      <c r="E10">
+        <v>2700000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
+        <v>الدخل التشغيلي - Operating Income (EBIT)</v>
       </c>
       <c r="B11">
-        <v>2100000000</v>
+        <v>6000000000</v>
+      </c>
+      <c r="C11">
+        <v>6600000000</v>
+      </c>
+      <c r="D11">
+        <v>6500000000</v>
+      </c>
+      <c r="E11">
+        <v>7200000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
+        <v>إيرادات الفوائد - Interest Income</v>
       </c>
       <c r="B12">
-        <v>2500000000</v>
+        <v>800000000</v>
+      </c>
+      <c r="C12">
+        <v>850000000</v>
+      </c>
+      <c r="D12">
+        <v>820000000</v>
+      </c>
+      <c r="E12">
+        <v>900000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>الدخل التشغيلي - Operating Income (EBIT)</v>
+        <v>مصروفات الفوائد - Interest Expense</v>
       </c>
       <c r="B13">
-        <v>6000000000</v>
+        <v>3200000000</v>
+      </c>
+      <c r="C13">
+        <v>3300000000</v>
+      </c>
+      <c r="D13">
+        <v>3150000000</v>
+      </c>
+      <c r="E13">
+        <v>3500000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>إيرادات الفوائد - Interest Income</v>
+        <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
       </c>
       <c r="B14">
-        <v>800000000</v>
+        <v>-400000000</v>
+      </c>
+      <c r="C14">
+        <v>-300000000</v>
+      </c>
+      <c r="D14">
+        <v>-500000000</v>
+      </c>
+      <c r="E14">
+        <v>-200000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>مصروفات الفوائد - Interest Expense</v>
+        <v>الدخل قبل الضريبة - Income Before Tax</v>
       </c>
       <c r="B15">
         <v>3200000000</v>
       </c>
+      <c r="C15">
+        <v>3850000000</v>
+      </c>
+      <c r="D15">
+        <v>3670000000</v>
+      </c>
+      <c r="E15">
+        <v>4400000000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
+        <v>مصروف ضريبة الدخل - Income Tax Expense</v>
       </c>
       <c r="B16">
-        <v>-400000000</v>
+        <v>480000000</v>
+      </c>
+      <c r="C16">
+        <v>577500000</v>
+      </c>
+      <c r="D16">
+        <v>550500000</v>
+      </c>
+      <c r="E16">
+        <v>660000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>الدخل قبل الضريبة - Income Before Tax</v>
+        <v>صافي الدخل - Net Income</v>
       </c>
       <c r="B17">
-        <v>3200000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>مصروف ضريبة الدخل - Income Tax Expense</v>
-      </c>
-      <c r="B18">
-        <v>480000000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>صافي الدخل - Net Income</v>
-      </c>
-      <c r="B19">
         <v>2720000000</v>
+      </c>
+      <c r="C17">
+        <v>3272500000</v>
+      </c>
+      <c r="D17">
+        <v>3119500000</v>
+      </c>
+      <c r="E17">
+        <v>3740000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:E17"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,156 +708,576 @@
         <v>البند Line Item</v>
       </c>
       <c r="B1" t="str">
-        <v>القيمة Value</v>
+        <v>Q1 2024</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Q2 2024</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Q3 2024</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Q4 2024</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>العملة Currency</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>SAR</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SAR</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>الفترة المالية Period</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Q1 2024</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>العملة Currency</v>
-      </c>
-      <c r="B4" t="str">
-        <v>SAR</v>
+        <v>الإيرادات - Revenue</v>
+      </c>
+      <c r="B4">
+        <v>8500000000</v>
+      </c>
+      <c r="C4">
+        <v>9200000000</v>
+      </c>
+      <c r="D4">
+        <v>8900000000</v>
+      </c>
+      <c r="E4">
+        <v>9800000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+        <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
+      </c>
+      <c r="B5">
+        <v>1800000000</v>
+      </c>
+      <c r="C5">
+        <v>1950000000</v>
+      </c>
+      <c r="D5">
+        <v>1900000000</v>
+      </c>
+      <c r="E5">
+        <v>2100000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>الإيرادات - Revenue</v>
+        <v>إجمالي الربح - Gross Profit</v>
       </c>
       <c r="B6">
-        <v>8500000000</v>
+        <v>6700000000</v>
+      </c>
+      <c r="C6">
+        <v>7250000000</v>
+      </c>
+      <c r="D6">
+        <v>7000000000</v>
+      </c>
+      <c r="E6">
+        <v>7700000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
+        <v>المصروفات التشغيلية - Operating Expenses</v>
       </c>
       <c r="B7">
-        <v>1800000000</v>
+        <v>3400000000</v>
+      </c>
+      <c r="C7">
+        <v>3600000000</v>
+      </c>
+      <c r="D7">
+        <v>3500000000</v>
+      </c>
+      <c r="E7">
+        <v>3800000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>إجمالي الربح - Gross Profit</v>
+        <v>مصروفات البيع - Selling Expenses</v>
       </c>
       <c r="B8">
-        <v>6700000000</v>
+        <v>700000000</v>
+      </c>
+      <c r="C8">
+        <v>750000000</v>
+      </c>
+      <c r="D8">
+        <v>720000000</v>
+      </c>
+      <c r="E8">
+        <v>800000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>المصروفات التشغيلية - Operating Expenses</v>
+        <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
       </c>
       <c r="B9">
-        <v>3400000000</v>
+        <v>1300000000</v>
+      </c>
+      <c r="C9">
+        <v>1350000000</v>
+      </c>
+      <c r="D9">
+        <v>1330000000</v>
+      </c>
+      <c r="E9">
+        <v>1400000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>مصروفات البيع - Selling Expenses</v>
+        <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
       </c>
       <c r="B10">
-        <v>700000000</v>
+        <v>1400000000</v>
+      </c>
+      <c r="C10">
+        <v>1500000000</v>
+      </c>
+      <c r="D10">
+        <v>1450000000</v>
+      </c>
+      <c r="E10">
+        <v>1600000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
+        <v>الدخل التشغيلي - Operating Income (EBIT)</v>
       </c>
       <c r="B11">
-        <v>1300000000</v>
+        <v>3300000000</v>
+      </c>
+      <c r="C11">
+        <v>3650000000</v>
+      </c>
+      <c r="D11">
+        <v>3500000000</v>
+      </c>
+      <c r="E11">
+        <v>3900000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
+        <v>إيرادات الفوائد - Interest Income</v>
       </c>
       <c r="B12">
-        <v>1400000000</v>
+        <v>500000000</v>
+      </c>
+      <c r="C12">
+        <v>530000000</v>
+      </c>
+      <c r="D12">
+        <v>510000000</v>
+      </c>
+      <c r="E12">
+        <v>560000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>الدخل التشغيلي - Operating Income (EBIT)</v>
+        <v>مصروفات الفوائد - Interest Expense</v>
       </c>
       <c r="B13">
-        <v>3300000000</v>
+        <v>1800000000</v>
+      </c>
+      <c r="C13">
+        <v>1900000000</v>
+      </c>
+      <c r="D13">
+        <v>1850000000</v>
+      </c>
+      <c r="E13">
+        <v>2000000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>إيرادات الفوائد - Interest Income</v>
+        <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
       </c>
       <c r="B14">
-        <v>500000000</v>
+        <v>-200000000</v>
+      </c>
+      <c r="C14">
+        <v>-150000000</v>
+      </c>
+      <c r="D14">
+        <v>-250000000</v>
+      </c>
+      <c r="E14">
+        <v>-100000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>مصروفات الفوائد - Interest Expense</v>
+        <v>الدخل قبل الضريبة - Income Before Tax</v>
       </c>
       <c r="B15">
         <v>1800000000</v>
       </c>
+      <c r="C15">
+        <v>2130000000</v>
+      </c>
+      <c r="D15">
+        <v>1910000000</v>
+      </c>
+      <c r="E15">
+        <v>2360000000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
+        <v>مصروف ضريبة الدخل - Income Tax Expense</v>
       </c>
       <c r="B16">
-        <v>-200000000</v>
+        <v>270000000</v>
+      </c>
+      <c r="C16">
+        <v>319500000</v>
+      </c>
+      <c r="D16">
+        <v>286500000</v>
+      </c>
+      <c r="E16">
+        <v>354000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>الدخل قبل الضريبة - Income Before Tax</v>
+        <v>صافي الدخل - Net Income</v>
       </c>
       <c r="B17">
-        <v>1800000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>مصروف ضريبة الدخل - Income Tax Expense</v>
-      </c>
-      <c r="B18">
-        <v>270000000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>صافي الدخل - Net Income</v>
-      </c>
-      <c r="B19">
         <v>1530000000</v>
+      </c>
+      <c r="C17">
+        <v>1810500000</v>
+      </c>
+      <c r="D17">
+        <v>1623500000</v>
+      </c>
+      <c r="E17">
+        <v>2006000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E17"/>
+  <cols>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>البند Line Item</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Q1 2024</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Q2 2024</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Q3 2024</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Q4 2024</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>العملة Currency</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SAR</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>الإيرادات - Revenue</v>
+      </c>
+      <c r="B4">
+        <v>12000000000</v>
+      </c>
+      <c r="C4">
+        <v>12800000000</v>
+      </c>
+      <c r="D4">
+        <v>12500000000</v>
+      </c>
+      <c r="E4">
+        <v>13500000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
+      </c>
+      <c r="B5">
+        <v>2600000000</v>
+      </c>
+      <c r="C5">
+        <v>2800000000</v>
+      </c>
+      <c r="D5">
+        <v>2700000000</v>
+      </c>
+      <c r="E5">
+        <v>3000000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>إجمالي الربح - Gross Profit</v>
+      </c>
+      <c r="B6">
+        <v>9400000000</v>
+      </c>
+      <c r="C6">
+        <v>10000000000</v>
+      </c>
+      <c r="D6">
+        <v>9800000000</v>
+      </c>
+      <c r="E6">
+        <v>10500000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>المصروفات التشغيلية - Operating Expenses</v>
+      </c>
+      <c r="B7">
+        <v>4600000000</v>
+      </c>
+      <c r="C7">
+        <v>4900000000</v>
+      </c>
+      <c r="D7">
+        <v>4700000000</v>
+      </c>
+      <c r="E7">
+        <v>5100000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>مصروفات البيع - Selling Expenses</v>
+      </c>
+      <c r="B8">
+        <v>1000000000</v>
+      </c>
+      <c r="C8">
+        <v>1050000000</v>
+      </c>
+      <c r="D8">
+        <v>1020000000</v>
+      </c>
+      <c r="E8">
+        <v>1100000000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
+      </c>
+      <c r="B9">
+        <v>1700000000</v>
+      </c>
+      <c r="C9">
+        <v>1800000000</v>
+      </c>
+      <c r="D9">
+        <v>1750000000</v>
+      </c>
+      <c r="E9">
+        <v>1900000000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
+      </c>
+      <c r="B10">
+        <v>1900000000</v>
+      </c>
+      <c r="C10">
+        <v>2050000000</v>
+      </c>
+      <c r="D10">
+        <v>1930000000</v>
+      </c>
+      <c r="E10">
+        <v>2100000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>الدخل التشغيلي - Operating Income (EBIT)</v>
+      </c>
+      <c r="B11">
+        <v>4800000000</v>
+      </c>
+      <c r="C11">
+        <v>5100000000</v>
+      </c>
+      <c r="D11">
+        <v>5100000000</v>
+      </c>
+      <c r="E11">
+        <v>5400000000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>إيرادات الفوائد - Interest Income</v>
+      </c>
+      <c r="B12">
+        <v>650000000</v>
+      </c>
+      <c r="C12">
+        <v>680000000</v>
+      </c>
+      <c r="D12">
+        <v>660000000</v>
+      </c>
+      <c r="E12">
+        <v>700000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>مصروفات الفوائد - Interest Expense</v>
+      </c>
+      <c r="B13">
+        <v>2400000000</v>
+      </c>
+      <c r="C13">
+        <v>2500000000</v>
+      </c>
+      <c r="D13">
+        <v>2450000000</v>
+      </c>
+      <c r="E13">
+        <v>2600000000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
+      </c>
+      <c r="B14">
+        <v>-350000000</v>
+      </c>
+      <c r="C14">
+        <v>-280000000</v>
+      </c>
+      <c r="D14">
+        <v>-400000000</v>
+      </c>
+      <c r="E14">
+        <v>-150000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>الدخل قبل الضريبة - Income Before Tax</v>
+      </c>
+      <c r="B15">
+        <v>2700000000</v>
+      </c>
+      <c r="C15">
+        <v>3000000000</v>
+      </c>
+      <c r="D15">
+        <v>2910000000</v>
+      </c>
+      <c r="E15">
+        <v>3350000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>مصروف ضريبة الدخل - Income Tax Expense</v>
+      </c>
+      <c r="B16">
+        <v>405000000</v>
+      </c>
+      <c r="C16">
+        <v>450000000</v>
+      </c>
+      <c r="D16">
+        <v>436500000</v>
+      </c>
+      <c r="E16">
+        <v>502500000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>صافي الدخل - Net Income</v>
+      </c>
+      <c r="B17">
+        <v>2295000000</v>
+      </c>
+      <c r="C17">
+        <v>2550000000</v>
+      </c>
+      <c r="D17">
+        <v>2473500000</v>
+      </c>
+      <c r="E17">
+        <v>2847500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/download/PnL_Sample_Data.xlsx
+++ b/download/PnL_Sample_Data.xlsx
@@ -399,13 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -413,16 +415,22 @@
         <v>البند Line Item</v>
       </c>
       <c r="B1" t="str">
-        <v>Q1 2024</v>
+        <v>Jan 2024</v>
       </c>
       <c r="C1" t="str">
-        <v>Q2 2024</v>
+        <v>Feb 2024</v>
       </c>
       <c r="D1" t="str">
-        <v>Q3 2024</v>
+        <v>Mar 2024</v>
       </c>
       <c r="E1" t="str">
-        <v>Q4 2024</v>
+        <v>Apr 2024</v>
+      </c>
+      <c r="F1" t="str">
+        <v>May 2024</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Jun 2024</v>
       </c>
     </row>
     <row r="2">
@@ -441,6 +449,12 @@
       <c r="E2" t="str">
         <v>SAR</v>
       </c>
+      <c r="F2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SAR</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -452,16 +466,22 @@
         <v>الإيرادات - Revenue</v>
       </c>
       <c r="B4">
-        <v>15000000000</v>
+        <v>5119044690</v>
       </c>
       <c r="C4">
-        <v>16200000000</v>
+        <v>5169691605</v>
       </c>
       <c r="D4">
-        <v>15800000000</v>
+        <v>4952562106</v>
       </c>
       <c r="E4">
-        <v>17500000000</v>
+        <v>4841098718</v>
+      </c>
+      <c r="F4">
+        <v>5138177521</v>
+      </c>
+      <c r="G4">
+        <v>4946313125</v>
       </c>
     </row>
     <row r="5">
@@ -469,16 +489,22 @@
         <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
       </c>
       <c r="B5">
-        <v>3200000000</v>
+        <v>1073096731</v>
       </c>
       <c r="C5">
-        <v>3500000000</v>
+        <v>1083038677</v>
       </c>
       <c r="D5">
-        <v>3400000000</v>
+        <v>1147427426</v>
       </c>
       <c r="E5">
-        <v>3800000000</v>
+        <v>1066414608</v>
+      </c>
+      <c r="F5">
+        <v>1143142632</v>
+      </c>
+      <c r="G5">
+        <v>1119000906</v>
       </c>
     </row>
     <row r="6">
@@ -486,16 +512,22 @@
         <v>إجمالي الربح - Gross Profit</v>
       </c>
       <c r="B6">
-        <v>11800000000</v>
+        <v>3857648626</v>
       </c>
       <c r="C6">
-        <v>12700000000</v>
+        <v>3996445822</v>
       </c>
       <c r="D6">
-        <v>12400000000</v>
+        <v>3907593817</v>
       </c>
       <c r="E6">
-        <v>13700000000</v>
+        <v>3957545222</v>
+      </c>
+      <c r="F6">
+        <v>3905359489</v>
+      </c>
+      <c r="G6">
+        <v>3956742834</v>
       </c>
     </row>
     <row r="7">
@@ -503,16 +535,22 @@
         <v>المصروفات التشغيلية - Operating Expenses</v>
       </c>
       <c r="B7">
-        <v>5800000000</v>
+        <v>1925865735</v>
       </c>
       <c r="C7">
-        <v>6100000000</v>
+        <v>1879923530</v>
       </c>
       <c r="D7">
-        <v>5900000000</v>
+        <v>1883589304</v>
       </c>
       <c r="E7">
-        <v>6500000000</v>
+        <v>1865540266</v>
+      </c>
+      <c r="F7">
+        <v>1887577850</v>
+      </c>
+      <c r="G7">
+        <v>1928918915</v>
       </c>
     </row>
     <row r="8">
@@ -520,16 +558,22 @@
         <v>مصروفات البيع - Selling Expenses</v>
       </c>
       <c r="B8">
-        <v>1200000000</v>
+        <v>403214776</v>
       </c>
       <c r="C8">
-        <v>1300000000</v>
+        <v>401489463</v>
       </c>
       <c r="D8">
-        <v>1250000000</v>
+        <v>384765061</v>
       </c>
       <c r="E8">
-        <v>1400000000</v>
+        <v>390827327</v>
+      </c>
+      <c r="F8">
+        <v>396591607</v>
+      </c>
+      <c r="G8">
+        <v>400090713</v>
       </c>
     </row>
     <row r="9">
@@ -537,16 +581,22 @@
         <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
       </c>
       <c r="B9">
-        <v>2100000000</v>
+        <v>713566240</v>
       </c>
       <c r="C9">
-        <v>2200000000</v>
+        <v>697751422</v>
       </c>
       <c r="D9">
-        <v>2150000000</v>
+        <v>717336071</v>
       </c>
       <c r="E9">
-        <v>2400000000</v>
+        <v>698880022</v>
+      </c>
+      <c r="F9">
+        <v>694614571</v>
+      </c>
+      <c r="G9">
+        <v>684453813</v>
       </c>
     </row>
     <row r="10">
@@ -554,16 +604,22 @@
         <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
       </c>
       <c r="B10">
-        <v>2500000000</v>
+        <v>784376024</v>
       </c>
       <c r="C10">
-        <v>2600000000</v>
+        <v>810724319</v>
       </c>
       <c r="D10">
-        <v>2500000000</v>
+        <v>785691230</v>
       </c>
       <c r="E10">
-        <v>2700000000</v>
+        <v>804931253</v>
+      </c>
+      <c r="F10">
+        <v>786470355</v>
+      </c>
+      <c r="G10">
+        <v>785936244</v>
       </c>
     </row>
     <row r="11">
@@ -571,16 +627,22 @@
         <v>الدخل التشغيلي - Operating Income (EBIT)</v>
       </c>
       <c r="B11">
-        <v>6000000000</v>
+        <v>1937801767</v>
       </c>
       <c r="C11">
-        <v>6600000000</v>
+        <v>2024448175</v>
       </c>
       <c r="D11">
-        <v>6500000000</v>
+        <v>1913275503</v>
       </c>
       <c r="E11">
-        <v>7200000000</v>
+        <v>1962165809</v>
+      </c>
+      <c r="F11">
+        <v>2068460052</v>
+      </c>
+      <c r="G11">
+        <v>2037824900</v>
       </c>
     </row>
     <row r="12">
@@ -588,16 +650,22 @@
         <v>إيرادات الفوائد - Interest Income</v>
       </c>
       <c r="B12">
-        <v>800000000</v>
+        <v>273909418</v>
       </c>
       <c r="C12">
-        <v>850000000</v>
+        <v>271257619</v>
       </c>
       <c r="D12">
-        <v>820000000</v>
+        <v>273588254</v>
       </c>
       <c r="E12">
-        <v>900000000</v>
+        <v>260789036</v>
+      </c>
+      <c r="F12">
+        <v>268973629</v>
+      </c>
+      <c r="G12">
+        <v>273362011</v>
       </c>
     </row>
     <row r="13">
@@ -605,16 +673,22 @@
         <v>مصروفات الفوائد - Interest Expense</v>
       </c>
       <c r="B13">
-        <v>3200000000</v>
+        <v>1123262581</v>
       </c>
       <c r="C13">
-        <v>3300000000</v>
+        <v>1110181271</v>
       </c>
       <c r="D13">
-        <v>3150000000</v>
+        <v>1106842721</v>
       </c>
       <c r="E13">
-        <v>3500000000</v>
+        <v>1120505094</v>
+      </c>
+      <c r="F13">
+        <v>1086117962</v>
+      </c>
+      <c r="G13">
+        <v>1101328857</v>
       </c>
     </row>
     <row r="14">
@@ -622,16 +696,22 @@
         <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
       </c>
       <c r="B14">
-        <v>-400000000</v>
+        <v>-126561684</v>
       </c>
       <c r="C14">
-        <v>-300000000</v>
+        <v>-122462076</v>
       </c>
       <c r="D14">
-        <v>-500000000</v>
+        <v>-128890062</v>
       </c>
       <c r="E14">
-        <v>-200000000</v>
+        <v>-121982451</v>
+      </c>
+      <c r="F14">
+        <v>-137073080</v>
+      </c>
+      <c r="G14">
+        <v>-123370657</v>
       </c>
     </row>
     <row r="15">
@@ -639,16 +719,22 @@
         <v>الدخل قبل الضريبة - Income Before Tax</v>
       </c>
       <c r="B15">
-        <v>3200000000</v>
+        <v>994680399</v>
       </c>
       <c r="C15">
-        <v>3850000000</v>
+        <v>1027820464</v>
       </c>
       <c r="D15">
-        <v>3670000000</v>
+        <v>1031633567</v>
       </c>
       <c r="E15">
-        <v>4400000000</v>
+        <v>1024159638</v>
+      </c>
+      <c r="F15">
+        <v>1037270487</v>
+      </c>
+      <c r="G15">
+        <v>1038573505</v>
       </c>
     </row>
     <row r="16">
@@ -656,16 +742,22 @@
         <v>مصروف ضريبة الدخل - Income Tax Expense</v>
       </c>
       <c r="B16">
-        <v>480000000</v>
+        <v>155659461</v>
       </c>
       <c r="C16">
-        <v>577500000</v>
+        <v>159805408</v>
       </c>
       <c r="D16">
-        <v>550500000</v>
+        <v>155648781</v>
       </c>
       <c r="E16">
-        <v>660000000</v>
+        <v>153459569</v>
+      </c>
+      <c r="F16">
+        <v>151070220</v>
+      </c>
+      <c r="G16">
+        <v>158713768</v>
       </c>
     </row>
     <row r="17">
@@ -673,34 +765,42 @@
         <v>صافي الدخل - Net Income</v>
       </c>
       <c r="B17">
-        <v>2720000000</v>
+        <v>920879228</v>
       </c>
       <c r="C17">
-        <v>3272500000</v>
+        <v>847893760</v>
       </c>
       <c r="D17">
-        <v>3119500000</v>
+        <v>841564436</v>
       </c>
       <c r="E17">
-        <v>3740000000</v>
+        <v>870924380</v>
+      </c>
+      <c r="F17">
+        <v>870430678</v>
+      </c>
+      <c r="G17">
+        <v>861363539</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,16 +808,22 @@
         <v>البند Line Item</v>
       </c>
       <c r="B1" t="str">
-        <v>Q1 2024</v>
+        <v>Jan 2024</v>
       </c>
       <c r="C1" t="str">
-        <v>Q2 2024</v>
+        <v>Feb 2024</v>
       </c>
       <c r="D1" t="str">
-        <v>Q3 2024</v>
+        <v>Mar 2024</v>
       </c>
       <c r="E1" t="str">
-        <v>Q4 2024</v>
+        <v>Apr 2024</v>
+      </c>
+      <c r="F1" t="str">
+        <v>May 2024</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Jun 2024</v>
       </c>
     </row>
     <row r="2">
@@ -736,6 +842,12 @@
       <c r="E2" t="str">
         <v>SAR</v>
       </c>
+      <c r="F2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SAR</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -747,16 +859,22 @@
         <v>الإيرادات - Revenue</v>
       </c>
       <c r="B4">
-        <v>8500000000</v>
+        <v>2836215216</v>
       </c>
       <c r="C4">
-        <v>9200000000</v>
+        <v>2730167818</v>
       </c>
       <c r="D4">
-        <v>8900000000</v>
+        <v>2797490514</v>
       </c>
       <c r="E4">
-        <v>9800000000</v>
+        <v>2814501797</v>
+      </c>
+      <c r="F4">
+        <v>2819054815</v>
+      </c>
+      <c r="G4">
+        <v>2872944282</v>
       </c>
     </row>
     <row r="5">
@@ -764,16 +882,22 @@
         <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
       </c>
       <c r="B5">
-        <v>1800000000</v>
+        <v>598737361</v>
       </c>
       <c r="C5">
-        <v>1950000000</v>
+        <v>609532249</v>
       </c>
       <c r="D5">
-        <v>1900000000</v>
+        <v>601044891</v>
       </c>
       <c r="E5">
-        <v>2100000000</v>
+        <v>626627261</v>
+      </c>
+      <c r="F5">
+        <v>571230357</v>
+      </c>
+      <c r="G5">
+        <v>583559173</v>
       </c>
     </row>
     <row r="6">
@@ -781,16 +905,22 @@
         <v>إجمالي الربح - Gross Profit</v>
       </c>
       <c r="B6">
-        <v>6700000000</v>
+        <v>2147643980</v>
       </c>
       <c r="C6">
-        <v>7250000000</v>
+        <v>2249847769</v>
       </c>
       <c r="D6">
-        <v>7000000000</v>
+        <v>2206430896</v>
       </c>
       <c r="E6">
-        <v>7700000000</v>
+        <v>2176006913</v>
+      </c>
+      <c r="F6">
+        <v>2125052429</v>
+      </c>
+      <c r="G6">
+        <v>2132073176</v>
       </c>
     </row>
     <row r="7">
@@ -798,16 +928,22 @@
         <v>المصروفات التشغيلية - Operating Expenses</v>
       </c>
       <c r="B7">
-        <v>3400000000</v>
+        <v>1112787397</v>
       </c>
       <c r="C7">
-        <v>3600000000</v>
+        <v>1085282870</v>
       </c>
       <c r="D7">
-        <v>3500000000</v>
+        <v>1122957596</v>
       </c>
       <c r="E7">
-        <v>3800000000</v>
+        <v>1114716746</v>
+      </c>
+      <c r="F7">
+        <v>1079252564</v>
+      </c>
+      <c r="G7">
+        <v>1117239955</v>
       </c>
     </row>
     <row r="8">
@@ -815,16 +951,22 @@
         <v>مصروفات البيع - Selling Expenses</v>
       </c>
       <c r="B8">
-        <v>700000000</v>
+        <v>222523212</v>
       </c>
       <c r="C8">
-        <v>750000000</v>
+        <v>228343183</v>
       </c>
       <c r="D8">
-        <v>720000000</v>
+        <v>234158978</v>
       </c>
       <c r="E8">
-        <v>800000000</v>
+        <v>221824379</v>
+      </c>
+      <c r="F8">
+        <v>223551308</v>
+      </c>
+      <c r="G8">
+        <v>221360089</v>
       </c>
     </row>
     <row r="9">
@@ -832,16 +974,22 @@
         <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
       </c>
       <c r="B9">
-        <v>1300000000</v>
+        <v>436764000</v>
       </c>
       <c r="C9">
-        <v>1350000000</v>
+        <v>426438021</v>
       </c>
       <c r="D9">
-        <v>1330000000</v>
+        <v>429098880</v>
       </c>
       <c r="E9">
-        <v>1400000000</v>
+        <v>428934431</v>
+      </c>
+      <c r="F9">
+        <v>420703613</v>
+      </c>
+      <c r="G9">
+        <v>420187938</v>
       </c>
     </row>
     <row r="10">
@@ -849,16 +997,22 @@
         <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
       </c>
       <c r="B10">
-        <v>1400000000</v>
+        <v>446255370</v>
       </c>
       <c r="C10">
-        <v>1500000000</v>
+        <v>444513414</v>
       </c>
       <c r="D10">
-        <v>1450000000</v>
+        <v>438897238</v>
       </c>
       <c r="E10">
-        <v>1600000000</v>
+        <v>447953491</v>
+      </c>
+      <c r="F10">
+        <v>441376332</v>
+      </c>
+      <c r="G10">
+        <v>437308036</v>
       </c>
     </row>
     <row r="11">
@@ -866,16 +1020,22 @@
         <v>الدخل التشغيلي - Operating Income (EBIT)</v>
       </c>
       <c r="B11">
-        <v>3300000000</v>
+        <v>1062230140</v>
       </c>
       <c r="C11">
-        <v>3650000000</v>
+        <v>1126653010</v>
       </c>
       <c r="D11">
-        <v>3500000000</v>
+        <v>1129499876</v>
       </c>
       <c r="E11">
-        <v>3900000000</v>
+        <v>1104593809</v>
+      </c>
+      <c r="F11">
+        <v>1083997400</v>
+      </c>
+      <c r="G11">
+        <v>1112481729</v>
       </c>
     </row>
     <row r="12">
@@ -883,16 +1043,22 @@
         <v>إيرادات الفوائد - Interest Income</v>
       </c>
       <c r="B12">
-        <v>500000000</v>
+        <v>166042483</v>
       </c>
       <c r="C12">
-        <v>530000000</v>
+        <v>175756088</v>
       </c>
       <c r="D12">
-        <v>510000000</v>
+        <v>165055131</v>
       </c>
       <c r="E12">
-        <v>560000000</v>
+        <v>168483281</v>
+      </c>
+      <c r="F12">
+        <v>175025222</v>
+      </c>
+      <c r="G12">
+        <v>174069340</v>
       </c>
     </row>
     <row r="13">
@@ -900,16 +1066,22 @@
         <v>مصروفات الفوائد - Interest Expense</v>
       </c>
       <c r="B13">
-        <v>1800000000</v>
+        <v>602890472</v>
       </c>
       <c r="C13">
-        <v>1900000000</v>
+        <v>587447642</v>
       </c>
       <c r="D13">
-        <v>1850000000</v>
+        <v>611346608</v>
       </c>
       <c r="E13">
-        <v>2000000000</v>
+        <v>598827830</v>
+      </c>
+      <c r="F13">
+        <v>602439462</v>
+      </c>
+      <c r="G13">
+        <v>588565582</v>
       </c>
     </row>
     <row r="14">
@@ -917,16 +1089,22 @@
         <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
       </c>
       <c r="B14">
-        <v>-200000000</v>
+        <v>-73426196</v>
       </c>
       <c r="C14">
-        <v>-150000000</v>
+        <v>-70724882</v>
       </c>
       <c r="D14">
-        <v>-250000000</v>
+        <v>-67152698</v>
       </c>
       <c r="E14">
-        <v>-100000000</v>
+        <v>-72454822</v>
+      </c>
+      <c r="F14">
+        <v>-73966104</v>
+      </c>
+      <c r="G14">
+        <v>-66279550</v>
       </c>
     </row>
     <row r="15">
@@ -934,16 +1112,22 @@
         <v>الدخل قبل الضريبة - Income Before Tax</v>
       </c>
       <c r="B15">
-        <v>1800000000</v>
+        <v>627149378</v>
       </c>
       <c r="C15">
-        <v>2130000000</v>
+        <v>580791306</v>
       </c>
       <c r="D15">
-        <v>1910000000</v>
+        <v>605352583</v>
       </c>
       <c r="E15">
-        <v>2360000000</v>
+        <v>593815726</v>
+      </c>
+      <c r="F15">
+        <v>627143676</v>
+      </c>
+      <c r="G15">
+        <v>621184525</v>
       </c>
     </row>
     <row r="16">
@@ -951,16 +1135,22 @@
         <v>مصروف ضريبة الدخل - Income Tax Expense</v>
       </c>
       <c r="B16">
-        <v>270000000</v>
+        <v>93382939</v>
       </c>
       <c r="C16">
-        <v>319500000</v>
+        <v>93576808</v>
       </c>
       <c r="D16">
-        <v>286500000</v>
+        <v>93584343</v>
       </c>
       <c r="E16">
-        <v>354000000</v>
+        <v>85579913</v>
+      </c>
+      <c r="F16">
+        <v>87889719</v>
+      </c>
+      <c r="G16">
+        <v>86956368</v>
       </c>
     </row>
     <row r="17">
@@ -968,34 +1158,42 @@
         <v>صافي الدخل - Net Income</v>
       </c>
       <c r="B17">
-        <v>1530000000</v>
+        <v>490833205</v>
       </c>
       <c r="C17">
-        <v>1810500000</v>
+        <v>505237836</v>
       </c>
       <c r="D17">
-        <v>1623500000</v>
+        <v>518259023</v>
       </c>
       <c r="E17">
-        <v>2006000000</v>
+        <v>504180984</v>
+      </c>
+      <c r="F17">
+        <v>517867745</v>
+      </c>
+      <c r="G17">
+        <v>484713468</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1003,16 +1201,22 @@
         <v>البند Line Item</v>
       </c>
       <c r="B1" t="str">
-        <v>Q1 2024</v>
+        <v>Jan 2024</v>
       </c>
       <c r="C1" t="str">
-        <v>Q2 2024</v>
+        <v>Feb 2024</v>
       </c>
       <c r="D1" t="str">
-        <v>Q3 2024</v>
+        <v>Mar 2024</v>
       </c>
       <c r="E1" t="str">
-        <v>Q4 2024</v>
+        <v>Apr 2024</v>
+      </c>
+      <c r="F1" t="str">
+        <v>May 2024</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Jun 2024</v>
       </c>
     </row>
     <row r="2">
@@ -1031,6 +1235,12 @@
       <c r="E2" t="str">
         <v>SAR</v>
       </c>
+      <c r="F2" t="str">
+        <v>SAR</v>
+      </c>
+      <c r="G2" t="str">
+        <v>SAR</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1042,16 +1252,22 @@
         <v>الإيرادات - Revenue</v>
       </c>
       <c r="B4">
-        <v>12000000000</v>
+        <v>3917549766</v>
       </c>
       <c r="C4">
-        <v>12800000000</v>
+        <v>3897950938</v>
       </c>
       <c r="D4">
-        <v>12500000000</v>
+        <v>3940168581</v>
       </c>
       <c r="E4">
-        <v>13500000000</v>
+        <v>4045936579</v>
+      </c>
+      <c r="F4">
+        <v>3912939904</v>
+      </c>
+      <c r="G4">
+        <v>4078547521</v>
       </c>
     </row>
     <row r="5">
@@ -1059,16 +1275,22 @@
         <v>تكلفة البضاعة المباعة - Cost of Goods Sold</v>
       </c>
       <c r="B5">
-        <v>2600000000</v>
+        <v>886738105</v>
       </c>
       <c r="C5">
-        <v>2800000000</v>
+        <v>891152522</v>
       </c>
       <c r="D5">
-        <v>2700000000</v>
+        <v>832809782</v>
       </c>
       <c r="E5">
-        <v>3000000000</v>
+        <v>838513775</v>
+      </c>
+      <c r="F5">
+        <v>885925940</v>
+      </c>
+      <c r="G5">
+        <v>864733241</v>
       </c>
     </row>
     <row r="6">
@@ -1076,16 +1298,22 @@
         <v>إجمالي الربح - Gross Profit</v>
       </c>
       <c r="B6">
-        <v>9400000000</v>
+        <v>3208217576</v>
       </c>
       <c r="C6">
-        <v>10000000000</v>
+        <v>3033189257</v>
       </c>
       <c r="D6">
-        <v>9800000000</v>
+        <v>3179410689</v>
       </c>
       <c r="E6">
-        <v>10500000000</v>
+        <v>3232350163</v>
+      </c>
+      <c r="F6">
+        <v>3137187771</v>
+      </c>
+      <c r="G6">
+        <v>3132858802</v>
       </c>
     </row>
     <row r="7">
@@ -1093,16 +1321,22 @@
         <v>المصروفات التشغيلية - Operating Expenses</v>
       </c>
       <c r="B7">
-        <v>4600000000</v>
+        <v>1503242822</v>
       </c>
       <c r="C7">
-        <v>4900000000</v>
+        <v>1491879033</v>
       </c>
       <c r="D7">
-        <v>4700000000</v>
+        <v>1519804660</v>
       </c>
       <c r="E7">
-        <v>5100000000</v>
+        <v>1573678898</v>
+      </c>
+      <c r="F7">
+        <v>1524448176</v>
+      </c>
+      <c r="G7">
+        <v>1509989267</v>
       </c>
     </row>
     <row r="8">
@@ -1110,16 +1344,22 @@
         <v>مصروفات البيع - Selling Expenses</v>
       </c>
       <c r="B8">
-        <v>1000000000</v>
+        <v>332872573</v>
       </c>
       <c r="C8">
-        <v>1050000000</v>
+        <v>333430461</v>
       </c>
       <c r="D8">
-        <v>1020000000</v>
+        <v>340762497</v>
       </c>
       <c r="E8">
-        <v>1100000000</v>
+        <v>323921007</v>
+      </c>
+      <c r="F8">
+        <v>327198860</v>
+      </c>
+      <c r="G8">
+        <v>324018031</v>
       </c>
     </row>
     <row r="9">
@@ -1127,16 +1367,22 @@
         <v>مصروفات إدارية وعمومية - General &amp; Administrative</v>
       </c>
       <c r="B9">
-        <v>1700000000</v>
+        <v>582678502</v>
       </c>
       <c r="C9">
-        <v>1800000000</v>
+        <v>575439063</v>
       </c>
       <c r="D9">
-        <v>1750000000</v>
+        <v>571262001</v>
       </c>
       <c r="E9">
-        <v>1900000000</v>
+        <v>564365694</v>
+      </c>
+      <c r="F9">
+        <v>557956480</v>
+      </c>
+      <c r="G9">
+        <v>571807719</v>
       </c>
     </row>
     <row r="10">
@@ -1144,16 +1390,22 @@
         <v>الإهلاك والاستنفاد - Depreciation &amp; Amortization</v>
       </c>
       <c r="B10">
-        <v>1900000000</v>
+        <v>618316130</v>
       </c>
       <c r="C10">
-        <v>2050000000</v>
+        <v>618405138</v>
       </c>
       <c r="D10">
-        <v>1930000000</v>
+        <v>626274859</v>
       </c>
       <c r="E10">
-        <v>2100000000</v>
+        <v>624255411</v>
+      </c>
+      <c r="F10">
+        <v>639760973</v>
+      </c>
+      <c r="G10">
+        <v>628551645</v>
       </c>
     </row>
     <row r="11">
@@ -1161,16 +1413,22 @@
         <v>الدخل التشغيلي - Operating Income (EBIT)</v>
       </c>
       <c r="B11">
-        <v>4800000000</v>
+        <v>1532203619</v>
       </c>
       <c r="C11">
-        <v>5100000000</v>
+        <v>1568683630</v>
       </c>
       <c r="D11">
-        <v>5100000000</v>
+        <v>1662189134</v>
       </c>
       <c r="E11">
-        <v>5400000000</v>
+        <v>1604778524</v>
+      </c>
+      <c r="F11">
+        <v>1556024790</v>
+      </c>
+      <c r="G11">
+        <v>1622663509</v>
       </c>
     </row>
     <row r="12">
@@ -1178,16 +1436,22 @@
         <v>إيرادات الفوائد - Interest Income</v>
       </c>
       <c r="B12">
-        <v>650000000</v>
+        <v>212869758</v>
       </c>
       <c r="C12">
-        <v>680000000</v>
+        <v>221714301</v>
       </c>
       <c r="D12">
-        <v>660000000</v>
+        <v>218695951</v>
       </c>
       <c r="E12">
-        <v>700000000</v>
+        <v>217233902</v>
+      </c>
+      <c r="F12">
+        <v>220250375</v>
+      </c>
+      <c r="G12">
+        <v>219355225</v>
       </c>
     </row>
     <row r="13">
@@ -1195,16 +1459,22 @@
         <v>مصروفات الفوائد - Interest Expense</v>
       </c>
       <c r="B13">
-        <v>2400000000</v>
+        <v>826724423</v>
       </c>
       <c r="C13">
-        <v>2500000000</v>
+        <v>824183590</v>
       </c>
       <c r="D13">
-        <v>2450000000</v>
+        <v>814274558</v>
       </c>
       <c r="E13">
-        <v>2600000000</v>
+        <v>823762823</v>
+      </c>
+      <c r="F13">
+        <v>836706818</v>
+      </c>
+      <c r="G13">
+        <v>822378345</v>
       </c>
     </row>
     <row r="14">
@@ -1212,16 +1482,22 @@
         <v>إيرادات/مصروفات أخرى - Other Income/Expense</v>
       </c>
       <c r="B14">
-        <v>-350000000</v>
+        <v>-106139758</v>
       </c>
       <c r="C14">
-        <v>-280000000</v>
+        <v>-102445985</v>
       </c>
       <c r="D14">
-        <v>-400000000</v>
+        <v>-99598461</v>
       </c>
       <c r="E14">
-        <v>-150000000</v>
+        <v>-106661012</v>
+      </c>
+      <c r="F14">
+        <v>-100666323</v>
+      </c>
+      <c r="G14">
+        <v>-103320950</v>
       </c>
     </row>
     <row r="15">
@@ -1229,16 +1505,22 @@
         <v>الدخل قبل الضريبة - Income Before Tax</v>
       </c>
       <c r="B15">
-        <v>2700000000</v>
+        <v>925615032</v>
       </c>
       <c r="C15">
-        <v>3000000000</v>
+        <v>890842639</v>
       </c>
       <c r="D15">
-        <v>2910000000</v>
+        <v>902300801</v>
       </c>
       <c r="E15">
-        <v>3350000000</v>
+        <v>926981608</v>
+      </c>
+      <c r="F15">
+        <v>876750918</v>
+      </c>
+      <c r="G15">
+        <v>921201245</v>
       </c>
     </row>
     <row r="16">
@@ -1246,16 +1528,22 @@
         <v>مصروف ضريبة الدخل - Income Tax Expense</v>
       </c>
       <c r="B16">
-        <v>405000000</v>
+        <v>132855527</v>
       </c>
       <c r="C16">
-        <v>450000000</v>
+        <v>132134367</v>
       </c>
       <c r="D16">
-        <v>436500000</v>
+        <v>135002647</v>
       </c>
       <c r="E16">
-        <v>502500000</v>
+        <v>140388712</v>
+      </c>
+      <c r="F16">
+        <v>135442318</v>
+      </c>
+      <c r="G16">
+        <v>137183590</v>
       </c>
     </row>
     <row r="17">
@@ -1263,21 +1551,27 @@
         <v>صافي الدخل - Net Income</v>
       </c>
       <c r="B17">
-        <v>2295000000</v>
+        <v>787807859</v>
       </c>
       <c r="C17">
-        <v>2550000000</v>
+        <v>743539342</v>
       </c>
       <c r="D17">
-        <v>2473500000</v>
+        <v>769995252</v>
       </c>
       <c r="E17">
-        <v>2847500000</v>
+        <v>762131521</v>
+      </c>
+      <c r="F17">
+        <v>785333273</v>
+      </c>
+      <c r="G17">
+        <v>760188791</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/download/PnL_Sample_Data.xlsx
+++ b/download/PnL_Sample_Data.xlsx
@@ -54,7 +54,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -80,7 +80,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B5E20"/>
         <bgColor rgb="001B5E20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D47A1"/>
+        <bgColor rgb="000D47A1"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,28 +155,31 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -539,10 +548,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="85" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,145 +574,159 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  هذا الملف يحتوي على بيانات نموذجية لثلاث شركات سعودية</t>
+          <t xml:space="preserve">  هذا الملف يحتوي على بيانات نموذجية لثلاث شركات سعودية لسنتين (2025 + 2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  كل ورقة تمثل شركة مستقلة ببيانات 6 أشهر (يناير - يونيو 2026)</t>
+          <t xml:space="preserve">  كل ورقة تمثل شركة مستقلة ببيانات 12 شهر (يناير - يونيو 2025 + يناير - يونيو 2026)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  يمكنك تعديل الأرقام أو إضافة شركات أخرى بأوراق جديدة</t>
+          <t xml:space="preserve">  الأعمدة الزرقاء = 2025 | الأعمدة الخضراء = 2026 — لدعم المقارنة السنوية</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  اسم الورقة = اسم الشركة</t>
+          <t xml:space="preserve">  يمكنك تعديل الأرقام أو إضافة شركات أخرى بأوراق جديدة</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  الصف 1: الفترات المالية  |  الصف 2: العملة  |  عمود A = اسم البند  |  الأعمدة B-G = القيم</t>
+          <t xml:space="preserve">  اسم الورقة = اسم الشركة</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  الصف 1: الفترات المالية  |  الصف 2: العملة  |  عمود A = اسم البند</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  ملاحظة: لا توجد ضريبة دخل — نظام الزكاة الشرعية ينطبق</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  البنود باللون الأخضر = أرباح | باللون الأصفر = إجماليات | بالأخضر الفاتح = أقسام</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>English:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This file contains sample data for three Saudi companies</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Each sheet represents one company with 6 months of data (Jan-Jun 2026)</t>
+          <t xml:space="preserve">  This file contains sample data for three Saudi companies for 2 years (2025 + 2026)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  You can edit numbers or add more companies in new sheets</t>
+          <t xml:space="preserve">  Each sheet = one company with 12 months (Jan-Jun 2025 + Jan-Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sheet name = Company name</t>
+          <t xml:space="preserve">  Blue columns = 2025 | Green columns = 2026 — enables year-over-year comparison</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Row 1: Periods  |  Row 2: Currency  |  Column A = Item name  |  Columns B-G = Values</t>
+          <t xml:space="preserve">  You can edit numbers or add more companies in new sheets</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sheet name = Company name</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Row 1: Periods  |  Row 2: Currency  |  Column A = Item name</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Note: No income tax — Islamic Zakat system applies</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Green cells = Profits | Yellow cells = Totals | Light green = Sections</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>الشركات النموذجية / Sample Companies:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. شركة النخبة التجارية — شركة تجارية (~8M ريال/شهر) — Trading company</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. شركة الأفق للخدمات — شركة خدماتية (~4.5M ريال/شهر) — Services company</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. شركة البناء الحديث — شركة صناعية/إنشائية (~12M ريال/شهر) — Construction company</t>
+          <t xml:space="preserve">  1. شركة النخبة التجارية — تجارية (~7M→8M ريال/شهر) — Trading (~14% YoY growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. شركة الأفق للخدمات — خدماتية (~4M→4.5M ريال/شهر) — Services (~12% YoY growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. شركة البناء الحديث — صناعية/إنشائية (~10M→12M ريال/شهر) — Construction (~19% YoY growth)</t>
         </is>
       </c>
     </row>
@@ -719,16 +742,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -737,1221 +766,2109 @@
           <t>البند Line Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>العملة Currency</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>الإيرادات - Revenue</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
+        <v>6192000</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>6450000</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>6708000</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>6966000</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>7310000</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>7654000</v>
+      </c>
+      <c r="H3" s="10" t="n">
         <v>7200000</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>7500000</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="J3" s="10" t="n">
         <v>7800000</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="K3" s="10" t="n">
         <v>8100000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="L3" s="10" t="n">
         <v>8500000</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="M3" s="10" t="n">
         <v>8900000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات المبيعات - Sales Revenue</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
+        <v>5590000</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>5848000</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>6020000</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>6278000</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>6622000</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>6880000</v>
+      </c>
+      <c r="H4" s="12" t="n">
         <v>6500000</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="I4" s="12" t="n">
         <v>6800000</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="J4" s="12" t="n">
         <v>7000000</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="K4" s="12" t="n">
         <v>7300000</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="L4" s="12" t="n">
         <v>7700000</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="M4" s="12" t="n">
         <v>8000000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الخدمات - Service Revenue</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
+        <v>430000</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>447200</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>473000</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>490200</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>473000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>516000</v>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="I5" s="12" t="n">
         <v>520000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="J5" s="12" t="n">
         <v>550000</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="K5" s="12" t="n">
         <v>570000</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="L5" s="12" t="n">
         <v>550000</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="M5" s="12" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Revenue</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
+        <v>172000</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>154800</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>215000</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>197800</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>215000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>258000</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <v>250000</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <v>230000</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <v>250000</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة البضاعة المباعة - Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
+        <v>3405600</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>3547500</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>3689400</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>3831300</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>4020500</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>4209700</v>
+      </c>
+      <c r="H7" s="14" t="n">
         <v>3960000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>4125000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>4290000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>4455000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>4675000</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>4895000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المواد الخام - Raw Materials</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
+        <v>1857600</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>1935000</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>2012400</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2089800</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2193000</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>2296200</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>2160000</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>2250000</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <v>2340000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <v>2430000</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="L8" s="12" t="n">
         <v>2550000</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="M8" s="12" t="n">
         <v>2670000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    العمالة المباشرة - Direct Labor</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
+        <v>774000</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>806250</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>838500</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>870750</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>913750</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>957825</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>900000</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <v>937500</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <v>975000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <v>1012500</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <v>1062500</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <v>1113750</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التصنيع غير المباشرة - Manufacturing Overhead</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
+        <v>464400</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>483750</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>503100</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>522450</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>548250</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>574695</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>562500</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>585000</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="K10" s="12" t="n">
         <v>607500</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="L10" s="12" t="n">
         <v>637500</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="M10" s="12" t="n">
         <v>668250</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المشتريات - Purchases</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
+        <v>309600</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>322500</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>335400</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>348300</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>365500</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>380980</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>360000</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>375000</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="J11" s="12" t="n">
         <v>390000</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>405000</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="L11" s="12" t="n">
         <v>425000</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="M11" s="12" t="n">
         <v>443000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>إجمالي الربح - Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
+        <v>2507760</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2612250</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>2716740</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>2821230</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>2960550</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>3099870</v>
+      </c>
+      <c r="H12" s="16" t="n">
         <v>3240000</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="I12" s="16" t="n">
         <v>3375000</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>3510000</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="K12" s="16" t="n">
         <v>3645000</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="L12" s="16" t="n">
         <v>3825000</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="M12" s="16" t="n">
         <v>4005000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>المصروفات التشغيلية - Operating Expenses</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="10" t="n">
+        <v>2167200</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>2257500</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>2347800</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>2438100</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2558500</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>2678900</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>2520000</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>2625000</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="J13" s="10" t="n">
         <v>2730000</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="K13" s="10" t="n">
         <v>2835000</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="L13" s="10" t="n">
         <v>2975000</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="M13" s="10" t="n">
         <v>3115000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات البيع والتسويق - Selling Expenses</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
+        <v>619200</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>645000</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>670800</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>696600</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>731000</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>765400</v>
+      </c>
+      <c r="H14" s="14" t="n">
         <v>720000</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>750000</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>780000</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>810000</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>850000</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="M14" s="14" t="n">
         <v>890000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    عمولات المبيعات - Sales Commissions</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
+        <v>167700</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>175440</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>180600</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>188340</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>198660</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>206400</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>195000</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <v>204000</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>210000</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>219000</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <v>231000</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <v>240000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإعلان والترويج - Advertising</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
+        <v>123840</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>129000</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>134160</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>139320</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>146200</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>153080</v>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>144000</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>156000</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>162000</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <v>170000</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <v>178000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التسويق - Marketing Expenses</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
+        <v>185760</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>193500</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>201240</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>208980</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>219300</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>229620</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>216000</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <v>225000</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>234000</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>243000</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <v>255000</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>267000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التوصيل والشحن - Delivery &amp; Shipping</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
+        <v>92880</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>96750</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>100620</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>104490</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>109650</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>114810</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>108000</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <v>112500</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <v>117000</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <v>121500</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>127500</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>133500</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    خدمة العملاء - Customer Service</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="12" t="n">
+        <v>49020</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>50310</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>54180</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>55470</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>57190</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>61490</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>57000</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <v>58500</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>63000</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>64500</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>66500</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <v>71500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  المصروفات الإدارية والعمومية - General &amp; Administrative</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
+        <v>1114560</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1161000</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1207440</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1253880</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1315800</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>1377720</v>
+      </c>
+      <c r="H20" s="14" t="n">
         <v>1296000</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="I20" s="14" t="n">
         <v>1350000</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="J20" s="14" t="n">
         <v>1404000</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="K20" s="14" t="n">
         <v>1458000</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="L20" s="14" t="n">
         <v>1530000</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="M20" s="14" t="n">
         <v>1602000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الرواتب والأجور - Salaries &amp; Wages</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
+        <v>513000</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>513000</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>513000</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>538650</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>538650</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>538650</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <v>567000</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>567000</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="M21" s="12" t="n">
         <v>567000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    بدلات ومزايا الموظفين - Employee Benefits</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="12" t="n">
+        <v>153900</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>153900</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>153900</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>161595</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>161595</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>161595</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>162000</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <v>162000</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <v>162000</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <v>170100</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="L22" s="12" t="n">
         <v>170100</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="M22" s="12" t="n">
         <v>170100</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    اشتراكات التأمينات الاجتماعية (GOSI) - GOSI Contributions</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="12" t="n">
+        <v>71820</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>71820</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>71820</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>75411</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>75411</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>75411</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>75600</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="I23" s="12" t="n">
         <v>75600</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="J23" s="12" t="n">
         <v>75600</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="K23" s="12" t="n">
         <v>79380</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="L23" s="12" t="n">
         <v>79380</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="M23" s="12" t="n">
         <v>79380</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإيجارات - Rent Expense</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="I24" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="J24" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="K24" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="L24" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="M24" s="12" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المرافق (كهرباء وماء وغاز) - Utilities</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="12" t="n">
+        <v>38700</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>36120</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>34400</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>41280</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>46440</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>49880</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="I25" s="12" t="n">
         <v>42000</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="J25" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="K25" s="12" t="n">
         <v>48000</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="L25" s="12" t="n">
         <v>54000</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="M25" s="12" t="n">
         <v>58000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاتصالات والإنترنت - Telecommunications</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>17100</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="I26" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="J26" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="K26" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="L26" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="M26" s="12" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    القرطاسية واللوازم المكتبية - Office Supplies</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
+        <v>10320</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>9890</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>8600</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>11180</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>10750</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>9460</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="I27" s="12" t="n">
         <v>11500</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="J27" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="K27" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="L27" s="12" t="n">
         <v>12500</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="M27" s="12" t="n">
         <v>11000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الأتعاب المهنية - Professional Fees</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
+        <v>51600</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>47300</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>64500</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>55900</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>68800</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <v>65000</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    السفر والضيافة - Travel &amp; Entertainment</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
+        <v>30100</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>25800</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>24080</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>38700</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>43000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>55900</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="I29" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="J29" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="K29" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="L29" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="M29" s="12" t="n">
         <v>65000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التأمين - Insurance Expense</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>22800</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>24000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="I30" s="12" t="n">
         <v>24000</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="J30" s="12" t="n">
         <v>24000</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="K30" s="12" t="n">
         <v>24000</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="L30" s="12" t="n">
         <v>24000</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="M30" s="12" t="n">
         <v>24000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الصيانة والإصلاحات - Maintenance &amp; Repairs</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="12" t="n">
+        <v>25800</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>30100</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>21500</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>34400</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>27520</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>32680</v>
+      </c>
+      <c r="H31" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="I31" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="J31" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="K31" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="L31" s="12" t="n">
         <v>32000</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="M31" s="12" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التراخيص والرسوم الحكومية - Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>8600</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>6880</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>10320</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>7740</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>6880</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="I32" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="J32" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="K32" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="L32" s="12" t="n">
         <v>9000</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="M32" s="12" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاشتراكات والبرمجيات - Subscriptions &amp; Software</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>34200</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="I33" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="J33" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="K33" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="L33" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="M33" s="12" t="n">
         <v>36000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الديون المعدومة - Bad Debts</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>62400</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="I34" s="12" t="n">
         <v>48000</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="J34" s="12" t="n">
         <v>52000</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="K34" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="L34" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="M34" s="12" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات متنوعة - Miscellaneous Expenses</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B35" s="12" t="n">
+        <v>66564</v>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>69574</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>72584</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>71827</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>75697</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>80427</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>77400</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="I35" s="12" t="n">
         <v>80900</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <v>84400</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="K35" s="12" t="n">
         <v>83520</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="L35" s="12" t="n">
         <v>88020</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="M35" s="12" t="n">
         <v>93520</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  الإهلاك والاستنفاد - Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
+        <v>309600</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>309600</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>309600</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>309600</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>322500</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>322500</v>
+      </c>
+      <c r="H36" s="14" t="n">
         <v>360000</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="I36" s="14" t="n">
         <v>360000</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="J36" s="14" t="n">
         <v>360000</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="K36" s="14" t="n">
         <v>360000</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="L36" s="14" t="n">
         <v>375000</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="M36" s="14" t="n">
         <v>375000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المباني - Depreciation of Buildings</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="I37" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="J37" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="K37" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="L37" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="M37" s="12" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المعدات والأجهزة - Depreciation of Equipment</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>171000</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="I38" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="J38" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="K38" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="L38" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="M38" s="12" t="n">
         <v>180000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك السيارات - Depreciation of Vehicles</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>71250</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>71250</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="I39" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="J39" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="K39" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="L39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="M39" s="12" t="n">
         <v>75000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    استنفاد الأصول غير الملموسة - Amortization of Intangibles</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="I40" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="J40" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="K40" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="L40" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="M40" s="12" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>الدخل التشغيلي - Operating Income (EBIT)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
+        <v>557280</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>580500</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>603720</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>626940</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>657900</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>688860</v>
+      </c>
+      <c r="H41" s="16" t="n">
         <v>720000</v>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="I41" s="16" t="n">
         <v>750000</v>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>780000</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="K41" s="16" t="n">
         <v>810000</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="L41" s="16" t="n">
         <v>850000</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="M41" s="16" t="n">
         <v>890000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الاستثمارات - Interest Income</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n">
+      <c r="B42" s="12" t="n">
+        <v>38700</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>36120</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>41280</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>47300</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>44720</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="I42" s="12" t="n">
         <v>42000</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="J42" s="12" t="n">
         <v>48000</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="K42" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="L42" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="M42" s="12" t="n">
         <v>52000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة التمويل - Finance Cost</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n">
+      <c r="B43" s="12" t="n">
+        <v>144000</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>138000</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>132000</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>126000</v>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="G43" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>115000</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <v>110000</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="K43" s="12" t="n">
         <v>105000</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="L43" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="M43" s="12" t="n">
         <v>95000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Income</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B44" s="12" t="n">
+        <v>25800</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>21500</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>30100</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>34400</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>24080</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>38700</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="I44" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="J44" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="K44" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="L44" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="M44" s="12" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات أخرى - Other Expenses</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B45" s="12" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>15480</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>10320</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>17200</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>12900</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>8600</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="I45" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="J45" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="K45" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="L45" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="M45" s="12" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>الدخل قبل الزكاة - Income Before Zakat</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="16" t="n">
+        <v>510840</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>529416</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>573534</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>599850</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>633132</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>682668</v>
+      </c>
+      <c r="H46" s="16" t="n">
         <v>660000</v>
       </c>
-      <c r="C46" s="15" t="n">
+      <c r="I46" s="16" t="n">
         <v>684000</v>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>741000</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="K46" s="16" t="n">
         <v>775000</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="L46" s="16" t="n">
         <v>818000</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="M46" s="16" t="n">
         <v>882000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروف الزكاة - Zakat Expense</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="12" t="n">
+        <v>14190</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>14706</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>15932</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>16662</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>17587</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>18963</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>16500</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="I47" s="12" t="n">
         <v>17100</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="J47" s="12" t="n">
         <v>18525</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="K47" s="12" t="n">
         <v>19375</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="L47" s="12" t="n">
         <v>20450</v>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="M47" s="12" t="n">
         <v>22050</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>صافي الدخل - Net Income</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B48" s="18" t="n">
+        <v>498069</v>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>516181</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>559196</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>584854</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>617304</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>665601</v>
+      </c>
+      <c r="H48" s="18" t="n">
         <v>643500</v>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="I48" s="18" t="n">
         <v>666900</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="J48" s="18" t="n">
         <v>722475</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="K48" s="18" t="n">
         <v>755625</v>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="L48" s="18" t="n">
         <v>797550</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="M48" s="18" t="n">
         <v>859950</v>
       </c>
     </row>
@@ -1967,16 +2884,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1985,1221 +2908,2109 @@
           <t>البند Line Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>العملة Currency</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>الإيرادات - Revenue</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
+        <v>3696000</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>3828000</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>4092000</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>4224000</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>4356000</v>
+      </c>
+      <c r="H3" s="10" t="n">
         <v>4200000</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>4350000</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="J3" s="10" t="n">
         <v>4500000</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="K3" s="10" t="n">
         <v>4650000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="L3" s="10" t="n">
         <v>4800000</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="M3" s="10" t="n">
         <v>4950000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات المبيعات - Sales Revenue</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>1144000</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>1188000</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>1232000</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="H4" s="12" t="n">
         <v>1200000</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="I4" s="12" t="n">
         <v>1250000</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="J4" s="12" t="n">
         <v>1300000</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="K4" s="12" t="n">
         <v>1350000</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="L4" s="12" t="n">
         <v>1400000</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="M4" s="12" t="n">
         <v>1450000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الخدمات - Service Revenue</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
+        <v>2464000</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>2552000</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>2728000</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>2816000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2904000</v>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>2800000</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="I5" s="12" t="n">
         <v>2900000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="J5" s="12" t="n">
         <v>3000000</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="K5" s="12" t="n">
         <v>3100000</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="L5" s="12" t="n">
         <v>3200000</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="M5" s="12" t="n">
         <v>3300000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Revenue</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>176000</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة البضاعة المباعة - Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
+        <v>1478400</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>1531200</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1584000</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1636800</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1689600</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1742400</v>
+      </c>
+      <c r="H7" s="14" t="n">
         <v>1680000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>1740000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>1800000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>1860000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>1920000</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>1980000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المواد الخام - Raw Materials</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
+        <v>369600</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>382800</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>396000</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>409200</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>422400</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>435600</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>420000</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>435000</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <v>450000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <v>465000</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="L8" s="12" t="n">
         <v>480000</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="M8" s="12" t="n">
         <v>495000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    العمالة المباشرة - Direct Labor</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
+        <v>554400</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>574200</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>594000</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>613800</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>633600</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>653400</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>630000</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <v>652500</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <v>675000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <v>697500</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <v>720000</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <v>742500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التصنيع غير المباشرة - Manufacturing Overhead</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
+        <v>295680</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>306240</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>316800</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>327360</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>337920</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>348480</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>336000</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>348000</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>360000</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="K10" s="12" t="n">
         <v>372000</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="L10" s="12" t="n">
         <v>384000</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="M10" s="12" t="n">
         <v>396000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المشتريات - Purchases</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
+        <v>258720</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>267960</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>277200</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>286440</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>295680</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>304920</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>294000</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>304500</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="J11" s="12" t="n">
         <v>315000</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>325500</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="L11" s="12" t="n">
         <v>336000</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="M11" s="12" t="n">
         <v>346500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>إجمالي الربح - Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
+        <v>1995840</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2067120</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>2138400</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>2209680</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>2280960</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>2352240</v>
+      </c>
+      <c r="H12" s="16" t="n">
         <v>2520000</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="I12" s="16" t="n">
         <v>2610000</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>2700000</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="K12" s="16" t="n">
         <v>2790000</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="L12" s="16" t="n">
         <v>2880000</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="M12" s="16" t="n">
         <v>2970000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>المصروفات التشغيلية - Operating Expenses</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="10" t="n">
+        <v>1663200</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>1722600</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1782000</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1841400</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>1900800</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>1960200</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>1890000</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>1957500</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="J13" s="10" t="n">
         <v>2025000</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="K13" s="10" t="n">
         <v>2092500</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="L13" s="10" t="n">
         <v>2160000</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="M13" s="10" t="n">
         <v>2227500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات البيع والتسويق - Selling Expenses</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
+        <v>332640</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>344520</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>356400</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>368280</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>380160</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>392040</v>
+      </c>
+      <c r="H14" s="14" t="n">
         <v>378000</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>391500</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>405000</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>418500</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>432000</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="M14" s="14" t="n">
         <v>445500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    عمولات المبيعات - Sales Commissions</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
+        <v>110880</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>114840</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>118800</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>122760</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>126720</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>130680</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>126000</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <v>130500</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>135000</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>139500</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <v>144000</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <v>148500</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإعلان والترويج - Advertising</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
+        <v>66528</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>68904</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>71280</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>73656</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>76032</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>78408</v>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>75600</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <v>78300</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>81000</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>83700</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <v>86400</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <v>89100</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التسويق - Marketing Expenses</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
+        <v>77616</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>80388</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>83160</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>85932</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>88704</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>91476</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>88200</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <v>91350</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>94500</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>97650</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <v>100800</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>103950</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التوصيل والشحن - Delivery &amp; Shipping</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
+        <v>44352</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>45936</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>47520</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>49104</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>50688</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>52272</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>50400</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <v>52200</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <v>54000</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <v>55800</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>57600</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>59400</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    خدمة العملاء - Customer Service</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="12" t="n">
+        <v>33264</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>34452</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>35640</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>36828</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>38016</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>39204</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>37800</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <v>39150</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>40500</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>41850</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>43200</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <v>44550</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  المصروفات الإدارية والعمومية - General &amp; Administrative</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
+        <v>997920</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1033560</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1069200</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1104840</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1140480</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>1176120</v>
+      </c>
+      <c r="H20" s="14" t="n">
         <v>1134000</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="I20" s="14" t="n">
         <v>1174500</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="J20" s="14" t="n">
         <v>1215000</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="K20" s="14" t="n">
         <v>1255500</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="L20" s="14" t="n">
         <v>1296000</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="M20" s="14" t="n">
         <v>1336500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الرواتب والأجور - Salaries &amp; Wages</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
+        <v>518400</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>518400</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>518400</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>544320</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>544320</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>544320</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <v>540000</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <v>567000</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>567000</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="M21" s="12" t="n">
         <v>567000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    بدلات ومزايا الموظفين - Employee Benefits</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="12" t="n">
+        <v>129600</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>129600</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>129600</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>136080</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>136080</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>136080</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>135000</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <v>135000</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <v>135000</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <v>141750</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="L22" s="12" t="n">
         <v>141750</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="M22" s="12" t="n">
         <v>141750</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    اشتراكات التأمينات الاجتماعية (GOSI) - GOSI Contributions</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="12" t="n">
+        <v>64800</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>64800</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>64800</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>68040</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>68040</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>68040</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>67500</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="I23" s="12" t="n">
         <v>67500</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="J23" s="12" t="n">
         <v>67500</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="K23" s="12" t="n">
         <v>70875</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="L23" s="12" t="n">
         <v>70875</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="M23" s="12" t="n">
         <v>70875</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإيجارات - Rent Expense</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="I24" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="J24" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="K24" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="L24" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="M24" s="12" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المرافق (كهرباء وماء وغاز) - Utilities</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="12" t="n">
+        <v>28160</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>26400</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>24640</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>30800</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>33440</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>36960</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>32000</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="I25" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="J25" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="K25" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="L25" s="12" t="n">
         <v>38000</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="M25" s="12" t="n">
         <v>42000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاتصالات والإنترنت - Telecommunications</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>14400</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="I26" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="J26" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="K26" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="L26" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="M26" s="12" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    القرطاسية واللوازم المكتبية - Office Supplies</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
+        <v>7040</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>6160</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>7480</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>7040</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="I27" s="12" t="n">
         <v>7500</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="J27" s="12" t="n">
         <v>7000</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="K27" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="L27" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="M27" s="12" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الأتعاب المهنية - Professional Fees</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
+        <v>39600</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>44000</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>35200</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>48400</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>52800</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>39600</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    السفر والضيافة - Travel &amp; Entertainment</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
+        <v>24640</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>19360</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>30800</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>35200</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>44000</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="I29" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="J29" s="12" t="n">
         <v>22000</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="K29" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="L29" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="M29" s="12" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التأمين - Insurance Expense</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="I30" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="J30" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="K30" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="L30" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="M30" s="12" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الصيانة والإصلاحات - Maintenance &amp; Repairs</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="12" t="n">
+        <v>17600</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>15840</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>26400</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>19360</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>24640</v>
+      </c>
+      <c r="H31" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="I31" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="J31" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="K31" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="L31" s="12" t="n">
         <v>22000</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="M31" s="12" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التراخيص والرسوم الحكومية - Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>7040</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>5280</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>6160</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>4400</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="I32" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="J32" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="K32" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="L32" s="12" t="n">
         <v>7000</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="M32" s="12" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاشتراكات والبرمجيات - Subscriptions &amp; Software</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>57600</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="I33" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="J33" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="K33" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="L33" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="M33" s="12" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الديون المعدومة - Bad Debts</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
+        <v>33600</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>38400</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>45600</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="I34" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="J34" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="K34" s="12" t="n">
         <v>32000</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="L34" s="12" t="n">
         <v>38000</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="M34" s="12" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات متنوعة - Miscellaneous Expenses</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B35" s="12" t="n">
+        <v>45320</v>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>47520</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>47410</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>48730</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>51370</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>51500</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="I35" s="12" t="n">
         <v>52500</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <v>54000</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="K35" s="12" t="n">
         <v>53875</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="L35" s="12" t="n">
         <v>55375</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="M35" s="12" t="n">
         <v>58375</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  الإهلاك والاستنفاد - Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>221760</v>
+      </c>
+      <c r="H36" s="14" t="n">
         <v>252000</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="I36" s="14" t="n">
         <v>252000</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="J36" s="14" t="n">
         <v>252000</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="K36" s="14" t="n">
         <v>252000</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="L36" s="14" t="n">
         <v>252000</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="M36" s="14" t="n">
         <v>252000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المباني - Depreciation of Buildings</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="I37" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="J37" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="K37" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="L37" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="M37" s="12" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المعدات والأجهزة - Depreciation of Equipment</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>115200</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="I38" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="J38" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="K38" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="L38" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="M38" s="12" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك السيارات - Depreciation of Vehicles</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>43200</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="I39" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="J39" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="K39" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="L39" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="M39" s="12" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    استنفاد الأصول غير الملموسة - Amortization of Intangibles</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>35520</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="I40" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="J40" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="K40" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="L40" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="M40" s="12" t="n">
         <v>37000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>الدخل التشغيلي - Operating Income (EBIT)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
+        <v>498960</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>516780</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>534600</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>552420</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>570240</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>588060</v>
+      </c>
+      <c r="H41" s="16" t="n">
         <v>630000</v>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="I41" s="16" t="n">
         <v>652500</v>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>675000</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="K41" s="16" t="n">
         <v>697500</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="L41" s="16" t="n">
         <v>720000</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="M41" s="16" t="n">
         <v>742500</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الاستثمارات - Interest Income</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n">
+      <c r="B42" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>20240</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>23760</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>24640</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>26400</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>25520</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="I42" s="12" t="n">
         <v>23000</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="J42" s="12" t="n">
         <v>27000</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="K42" s="12" t="n">
         <v>28000</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="L42" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="M42" s="12" t="n">
         <v>29000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة التمويل - Finance Cost</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n">
+      <c r="B43" s="12" t="n">
+        <v>96000</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>93600</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>84000</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>81600</v>
+      </c>
+      <c r="H43" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="I43" s="12" t="n">
         <v>78000</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="K43" s="12" t="n">
         <v>72000</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="L43" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="M43" s="12" t="n">
         <v>68000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Income</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B44" s="12" t="n">
+        <v>13200</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>15840</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>10560</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>17600</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>14080</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>19360</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="I44" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="J44" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="K44" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="L44" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="M44" s="12" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات أخرى - Other Expenses</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B45" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>10560</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>7040</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>12320</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>7040</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="I45" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="J45" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="K45" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="L45" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="M45" s="12" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>الدخل قبل الزكاة - Income Before Zakat</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="16" t="n">
+        <v>459360</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>477972</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>499752</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>522324</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>543312</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>568260</v>
+      </c>
+      <c r="H46" s="16" t="n">
         <v>580000</v>
       </c>
-      <c r="C46" s="15" t="n">
+      <c r="I46" s="16" t="n">
         <v>603500</v>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>631000</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="K46" s="16" t="n">
         <v>659500</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="L46" s="16" t="n">
         <v>686000</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="M46" s="16" t="n">
         <v>717500</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروف الزكاة - Zakat Expense</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="12" t="n">
+        <v>12760</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>13277</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>13882</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>14509</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>15092</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>15785</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>14500</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="I47" s="12" t="n">
         <v>15088</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="J47" s="12" t="n">
         <v>15775</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="K47" s="12" t="n">
         <v>16488</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="L47" s="12" t="n">
         <v>17150</v>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="M47" s="12" t="n">
         <v>17938</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>صافي الدخل - Net Income</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B48" s="18" t="n">
+        <v>447876</v>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>466023</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>487258</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>509266</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>529729</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>554054</v>
+      </c>
+      <c r="H48" s="18" t="n">
         <v>565500</v>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="I48" s="18" t="n">
         <v>588413</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="J48" s="18" t="n">
         <v>615225</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="K48" s="18" t="n">
         <v>643013</v>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="L48" s="18" t="n">
         <v>668850</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="M48" s="18" t="n">
         <v>699563</v>
       </c>
     </row>
@@ -3215,16 +5026,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3233,1221 +5050,2109 @@
           <t>البند Line Item</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2025</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feb 2025</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>May 2025</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>العملة Currency</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>الإيرادات - Revenue</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
+        <v>9660000</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>9912000</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>10920000</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>11340000</v>
+      </c>
+      <c r="H3" s="10" t="n">
         <v>11500000</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>12000000</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="J3" s="10" t="n">
         <v>11800000</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="K3" s="10" t="n">
         <v>12500000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="L3" s="10" t="n">
         <v>13000000</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="M3" s="10" t="n">
         <v>13500000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات المبيعات - Sales Revenue</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
+        <v>8820000</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>9240000</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>9072000</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>9660000</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>10500000</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="H4" s="12" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="I4" s="12" t="n">
         <v>11000000</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="J4" s="12" t="n">
         <v>10800000</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="K4" s="12" t="n">
         <v>11500000</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="L4" s="12" t="n">
         <v>12000000</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="M4" s="12" t="n">
         <v>12500000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الخدمات - Service Revenue</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>672000</v>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="I5" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="J5" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="K5" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="L5" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="M5" s="12" t="n">
         <v>800000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Revenue</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>168000</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة البضاعة المباعة - Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
+        <v>5796000</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>6048000</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>5947200</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>6552000</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>6804000</v>
+      </c>
+      <c r="H7" s="14" t="n">
         <v>6900000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>7200000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>7080000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>7500000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>7800000</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>8100000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المواد الخام - Raw Materials</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
+        <v>3864000</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>4032000</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>3964800</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>4368000</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>4536000</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>4600000</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>4800000</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <v>4720000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <v>5000000</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="L8" s="12" t="n">
         <v>5200000</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="M8" s="12" t="n">
         <v>5400000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    العمالة المباشرة - Direct Labor</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
+        <v>1159200</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>1209600</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>1189440</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>1310400</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1360800</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>1380000</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <v>1440000</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <v>1416000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <v>1500000</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <v>1560000</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <v>1620000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التصنيع غير المباشرة - Manufacturing Overhead</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
+        <v>483000</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>504000</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>495600</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>525000</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>546000</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>567000</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>575000</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>600000</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>590000</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="K10" s="12" t="n">
         <v>625000</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="L10" s="12" t="n">
         <v>650000</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="M10" s="12" t="n">
         <v>675000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المشتريات - Purchases</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
+        <v>289800</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>302400</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>297360</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>315000</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>327600</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>340200</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>345000</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>360000</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="J11" s="12" t="n">
         <v>354000</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>375000</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="L11" s="12" t="n">
         <v>390000</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="M11" s="12" t="n">
         <v>405000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>إجمالي الربح - Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
+        <v>3477600</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>3628800</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>3568320</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>3780000</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>3931200</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>4082400</v>
+      </c>
+      <c r="H12" s="16" t="n">
         <v>4600000</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="I12" s="16" t="n">
         <v>4800000</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="J12" s="16" t="n">
         <v>4720000</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="K12" s="16" t="n">
         <v>5000000</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="L12" s="16" t="n">
         <v>5200000</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="M12" s="16" t="n">
         <v>5400000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>المصروفات التشغيلية - Operating Expenses</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="10" t="n">
+        <v>2704800</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>2822400</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>2775360</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>2940000</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>3057600</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>3175200</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>3220000</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>3360000</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="J13" s="10" t="n">
         <v>3304000</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="K13" s="10" t="n">
         <v>3500000</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="L13" s="10" t="n">
         <v>3640000</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="M13" s="10" t="n">
         <v>3780000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات البيع والتسويق - Selling Expenses</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
+        <v>676200</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>705600</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>693840</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>735000</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>764400</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>793800</v>
+      </c>
+      <c r="H14" s="14" t="n">
         <v>805000</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>840000</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>826000</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>875000</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>910000</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="M14" s="14" t="n">
         <v>945000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    عمولات المبيعات - Sales Commissions</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
+        <v>202860</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>211680</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>208152</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>220500</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>229320</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>238140</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>241500</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <v>252000</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>247800</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>262500</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <v>273000</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <v>283500</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإعلان والترويج - Advertising</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
+        <v>135240</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>141120</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>138768</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>147000</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>152880</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>158760</v>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>161000</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <v>168000</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>165200</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>175000</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <v>182000</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <v>189000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات التسويق - Marketing Expenses</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
+        <v>202860</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>211680</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>208152</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>220500</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>229320</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>238140</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>241500</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <v>252000</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>247800</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>262500</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <v>273000</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>283500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التوصيل والشحن - Delivery &amp; Shipping</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
+        <v>101430</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>105840</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>104076</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>110250</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>114660</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>119070</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>120750</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <v>126000</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <v>123900</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <v>131250</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>136500</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>141750</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    خدمة العملاء - Customer Service</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="12" t="n">
+        <v>33810</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>35280</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>34692</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>36750</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>38220</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>39690</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>40250</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <v>42000</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <v>41300</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <v>43750</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>45500</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <v>47250</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  المصروفات الإدارية والعمومية - General &amp; Administrative</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
+        <v>1545600</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1612800</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1585920</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1747200</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>1814400</v>
+      </c>
+      <c r="H20" s="14" t="n">
         <v>1840000</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="I20" s="14" t="n">
         <v>1920000</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="J20" s="14" t="n">
         <v>1888000</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="K20" s="14" t="n">
         <v>2000000</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="L20" s="14" t="n">
         <v>2080000</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="M20" s="14" t="n">
         <v>2160000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الرواتب والأجور - Salaries &amp; Wages</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="12" t="n">
+        <v>705000</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>705000</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>705000</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>740250</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>740250</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>740250</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <v>787500</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>787500</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="M21" s="12" t="n">
         <v>787500</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    بدلات ومزايا الموظفين - Employee Benefits</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="12" t="n">
+        <v>211500</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>211500</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>211500</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>222075</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>222075</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>222075</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>225000</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <v>225000</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <v>225000</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <v>236250</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="L22" s="12" t="n">
         <v>236250</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="M22" s="12" t="n">
         <v>236250</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    اشتراكات التأمينات الاجتماعية (GOSI) - GOSI Contributions</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="12" t="n">
+        <v>98700</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>98700</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>98700</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>103635</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>103635</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>103635</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>105000</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="I23" s="12" t="n">
         <v>105000</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="J23" s="12" t="n">
         <v>105000</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="K23" s="12" t="n">
         <v>110250</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="L23" s="12" t="n">
         <v>110250</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="M23" s="12" t="n">
         <v>110250</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الإيجارات - Rent Expense</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>188000</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="I24" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="J24" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="K24" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="L24" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="M24" s="12" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    المرافق (كهرباء وماء وغاز) - Utilities</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="12" t="n">
+        <v>71400</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>67200</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>63000</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>79800</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>92400</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>100800</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>85000</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="I25" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="J25" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="K25" s="12" t="n">
         <v>95000</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="L25" s="12" t="n">
         <v>110000</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="M25" s="12" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاتصالات والإنترنت - Telecommunications</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="I26" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="J26" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="K26" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="L26" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="M26" s="12" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    القرطاسية واللوازم المكتبية - Office Supplies</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
+        <v>15120</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>14280</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>13440</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>15960</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>15120</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="I27" s="12" t="n">
         <v>17000</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="J27" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="K27" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="L27" s="12" t="n">
         <v>19000</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="M27" s="12" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الأتعاب المهنية - Professional Fees</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
+        <v>75600</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>71400</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>79800</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>67200</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>84000</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>92400</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <v>85000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <v>95000</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <v>110000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    السفر والضيافة - Travel &amp; Entertainment</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>37800</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>35280</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>50400</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>54600</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>63000</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="I29" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="J29" s="12" t="n">
         <v>42000</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="K29" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="L29" s="12" t="n">
         <v>65000</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="M29" s="12" t="n">
         <v>75000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التأمين - Insurance Expense</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>32900</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="I30" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="J30" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="K30" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="L30" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="M30" s="12" t="n">
         <v>35000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الصيانة والإصلاحات - Maintenance &amp; Repairs</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>50400</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>40320</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>58800</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>54600</v>
+      </c>
+      <c r="H31" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="I31" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="J31" s="12" t="n">
         <v>48000</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="K31" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="L31" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="M31" s="12" t="n">
         <v>65000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    التراخيص والرسوم الحكومية - Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
+        <v>16800</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>12600</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>10080</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>15120</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>11760</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="I32" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="J32" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="K32" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="L32" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="M32" s="12" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الاشتراكات والبرمجيات - Subscriptions &amp; Software</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>37600</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="I33" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="J33" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="K33" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="L33" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="M33" s="12" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    الديون المعدومة - Bad Debts</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
+        <v>84000</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>96000</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>86400</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>102000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>108000</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="I34" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="J34" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="K34" s="12" t="n">
         <v>72000</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="L34" s="12" t="n">
         <v>85000</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="M34" s="12" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    مصروفات متنوعة - Miscellaneous Expenses</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B35" s="12" t="n">
+        <v>68880</v>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>71400</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>68040</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>73920</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>76860</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>80640</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>82000</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="I35" s="12" t="n">
         <v>85000</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <v>81000</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="K35" s="12" t="n">
         <v>88000</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="L35" s="12" t="n">
         <v>91500</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="M35" s="12" t="n">
         <v>96000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  الإهلاك والاستنفاد - Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
+        <v>483000</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>504000</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>495600</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>525000</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>546000</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>567000</v>
+      </c>
+      <c r="H36" s="14" t="n">
         <v>575000</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="I36" s="14" t="n">
         <v>600000</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="J36" s="14" t="n">
         <v>590000</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="K36" s="14" t="n">
         <v>625000</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="L36" s="14" t="n">
         <v>650000</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="M36" s="14" t="n">
         <v>675000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المباني - Depreciation of Buildings</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="I37" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="J37" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="K37" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="L37" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="M37" s="12" t="n">
         <v>150000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك المعدات والأجهزة - Depreciation of Equipment</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="I38" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="J38" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="K38" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="L38" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="M38" s="12" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    إهلاك السيارات - Depreciation of Vehicles</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="I39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="J39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="K39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="L39" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="M39" s="12" t="n">
         <v>75000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">    استنفاد الأصول غير الملموسة - Amortization of Intangibles</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="12" t="n">
+        <v>47000</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>70500</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>61100</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>94000</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>117500</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>141000</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="I40" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="J40" s="12" t="n">
         <v>65000</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="K40" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="L40" s="12" t="n">
         <v>125000</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="M40" s="12" t="n">
         <v>150000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>الدخل التشغيلي - Operating Income (EBIT)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
+        <v>1043280</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>1088640</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>1070496</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>1134000</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>1179360</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>1224720</v>
+      </c>
+      <c r="H41" s="16" t="n">
         <v>1380000</v>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="I41" s="16" t="n">
         <v>1440000</v>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="J41" s="16" t="n">
         <v>1416000</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="K41" s="16" t="n">
         <v>1500000</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="L41" s="16" t="n">
         <v>1560000</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="M41" s="16" t="n">
         <v>1620000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات الاستثمارات - Interest Income</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n">
+      <c r="B42" s="12" t="n">
+        <v>50400</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>54600</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>58800</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>58800</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="I42" s="12" t="n">
         <v>55000</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="J42" s="12" t="n">
         <v>65000</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="K42" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="L42" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="M42" s="12" t="n">
         <v>70000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  تكلفة التمويل - Finance Cost</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n">
+      <c r="B43" s="12" t="n">
+        <v>216000</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>204000</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>198000</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>192000</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>186000</v>
+      </c>
+      <c r="H43" s="12" t="n">
         <v>180000</v>
       </c>
-      <c r="C43" s="11" t="n">
+      <c r="I43" s="12" t="n">
         <v>175000</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <v>170000</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="K43" s="12" t="n">
         <v>165000</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="L43" s="12" t="n">
         <v>160000</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="M43" s="12" t="n">
         <v>155000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  إيرادات أخرى - Other Income</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B44" s="12" t="n">
+        <v>33600</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>29400</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>37800</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>46200</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="I44" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="J44" s="12" t="n">
         <v>45000</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="K44" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="L44" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="M44" s="12" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروفات أخرى - Other Expenses</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B45" s="12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>25200</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>16800</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>29400</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>12600</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="I45" s="12" t="n">
         <v>30000</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="J45" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="K45" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="L45" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="M45" s="12" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>الدخل قبل الزكاة - Income Before Zakat</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="16" t="n">
+        <v>963900</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>1001700</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>1010016</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>1073520</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>1118880</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>1190700</v>
+      </c>
+      <c r="H46" s="16" t="n">
         <v>1275000</v>
       </c>
-      <c r="C46" s="15" t="n">
+      <c r="I46" s="16" t="n">
         <v>1325000</v>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="J46" s="16" t="n">
         <v>1336000</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="K46" s="16" t="n">
         <v>1420000</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="L46" s="16" t="n">
         <v>1480000</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="M46" s="16" t="n">
         <v>1575000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  مصروف الزكاة - Zakat Expense</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="12" t="n">
+        <v>26775</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>27825</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>28056</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>29820</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>31080</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>33075</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>31875</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="I47" s="12" t="n">
         <v>33125</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="J47" s="12" t="n">
         <v>33400</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="K47" s="12" t="n">
         <v>35500</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="L47" s="12" t="n">
         <v>37000</v>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="M47" s="12" t="n">
         <v>39375</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>صافي الدخل - Net Income</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B48" s="18" t="n">
+        <v>939802</v>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>976658</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>984766</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>1046682</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>1090908</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>1160932</v>
+      </c>
+      <c r="H48" s="18" t="n">
         <v>1243125</v>
       </c>
-      <c r="C48" s="17" t="n">
+      <c r="I48" s="18" t="n">
         <v>1291875</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="J48" s="18" t="n">
         <v>1302600</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="K48" s="18" t="n">
         <v>1384500</v>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="L48" s="18" t="n">
         <v>1443000</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="M48" s="18" t="n">
         <v>1535625</v>
       </c>
     </row>
